--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:19</t>
+    <t xml:space="preserve">2026-09-09 23:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:15</t>
+    <t xml:space="preserve">2026-09-17 14:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:10</t>
+    <t xml:space="preserve">2026-09-23 12:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:39</t>
+    <t xml:space="preserve">2026-10-02 14:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:04</t>
+    <t xml:space="preserve">2026-10-05 11:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
